--- a/MiniTemplate/Datas/convenience.xlsx
+++ b/MiniTemplate/Datas/convenience.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508059E6-E70D-4CA5-ACE1-055FC75FD3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3123E2-5366-4250-AF8A-7871DC7286E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31200" yWindow="-7236" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -63,10 +63,6 @@
     <t>名称</t>
   </si>
   <si>
-    <t>神秘礼盒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>price</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,18 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>神秘礼盒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IT技能证书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修技能证书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>时间币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,6 +108,48 @@
   </si>
   <si>
     <t>权重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初级零工凭证礼盒</t>
+  </si>
+  <si>
+    <t>初级零工凭证礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地铁卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转盘币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秘匣币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星阵币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时委托单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作通行券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别邀请函</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目投标书</t>
+  </si>
+  <si>
+    <t>传奇推荐信</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,18 +485,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="18.875" customWidth="1"/>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -481,19 +507,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -504,19 +530,19 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -530,16 +556,16 @@
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -550,196 +576,336 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1">
         <v>3000</v>
       </c>
       <c r="E5" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E6">
-        <v>888</v>
+        <v>1500</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>3000</v>
       </c>
       <c r="E7">
-        <v>1288</v>
+        <v>2000</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E8">
-        <v>1588</v>
+        <v>400</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>4000</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>4001</v>
+        <v>102</v>
       </c>
       <c r="E10">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>102</v>
       </c>
       <c r="E11">
-        <v>488</v>
+        <v>600</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12">
-        <v>102</v>
+        <v>4028</v>
       </c>
       <c r="E12">
-        <v>688</v>
+        <v>1000</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13">
-        <v>888</v>
+        <v>500</v>
       </c>
       <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14">
         <v>10</v>
       </c>
-      <c r="G13">
-        <v>900</v>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <v>105</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
+        <v>106</v>
+      </c>
+      <c r="E15">
+        <v>2000</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>4023</v>
+      </c>
+      <c r="E16">
+        <v>600</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>4024</v>
+      </c>
+      <c r="E17">
+        <v>800</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>4025</v>
+      </c>
+      <c r="E18">
+        <v>1200</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19">
+        <v>4026</v>
+      </c>
+      <c r="E19">
+        <v>2000</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20">
+        <v>4027</v>
+      </c>
+      <c r="E20">
+        <v>3000</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/convenience.xlsx
+++ b/MiniTemplate/Datas/convenience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3123E2-5366-4250-AF8A-7871DC7286E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F38AD2-ED17-4FF8-82A7-F2B240DECEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-7236" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
         <v>102</v>
       </c>
       <c r="E9">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -699,7 +699,7 @@
         <v>102</v>
       </c>
       <c r="E10">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -719,7 +719,7 @@
         <v>102</v>
       </c>
       <c r="E11">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -765,7 +765,7 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -785,7 +785,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">

--- a/MiniTemplate/Datas/convenience.xlsx
+++ b/MiniTemplate/Datas/convenience.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F38AD2-ED17-4FF8-82A7-F2B240DECEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34596A1D-D020-43E7-8311-F9F911F7754A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -118,10 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地铁卡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>转盘币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,6 +146,18 @@
   </si>
   <si>
     <t>传奇推荐信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鱼干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级零工凭证礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初级材料礼盒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,18 +493,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -565,7 +573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -588,7 +596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -599,16 +607,16 @@
         <v>3000</v>
       </c>
       <c r="E5" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -619,16 +627,16 @@
         <v>3000</v>
       </c>
       <c r="E6">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -639,56 +647,56 @@
         <v>3000</v>
       </c>
       <c r="E7">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>2000</v>
+        <v>3001</v>
       </c>
       <c r="E8">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>102</v>
+        <v>2000</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>6</v>
       </c>
@@ -699,16 +707,16 @@
         <v>102</v>
       </c>
       <c r="E10">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>7</v>
       </c>
@@ -719,41 +727,41 @@
         <v>102</v>
       </c>
       <c r="E11">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>4028</v>
+        <v>102</v>
       </c>
       <c r="E12">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>104</v>
@@ -768,12 +776,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>105</v>
@@ -788,12 +796,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>106</v>
@@ -808,12 +816,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>4023</v>
@@ -828,12 +836,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>4024</v>
@@ -848,12 +856,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>4025</v>
@@ -868,12 +876,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>4026</v>
@@ -888,12 +896,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>4027</v>
@@ -906,6 +914,46 @@
       </c>
       <c r="G20">
         <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>5005</v>
+      </c>
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>101</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22">
+        <v>3020</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
